--- a/_reference-materials/Necklace_Full_Spec_IT.xlsx
+++ b/_reference-materials/Necklace_Full_Spec_IT.xlsx
@@ -7,17 +7,16 @@
     <sheet sheetId="1" name="Prices" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Products" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Cord colours" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Colour palettes" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Sizes" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Shapy Shine shapes" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Notes for IT" state="visible" r:id="rId10"/>
+    <sheet sheetId="4" name="Sizes" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Shapes" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Notes for IT" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="129">
   <si>
     <t>Product ID</t>
   </si>
@@ -40,10 +39,10 @@
     <t>Min order qty</t>
   </si>
   <si>
-    <t>Price list 2025</t>
-  </si>
-  <si>
-    <t>Price list 2026</t>
+    <t>Price list 2025 (€)</t>
+  </si>
+  <si>
+    <t>Price list 2026 (€)</t>
   </si>
   <si>
     <t>Notes</t>
@@ -61,13 +60,7 @@
     <t>IGI</t>
   </si>
   <si>
-    <t>Same as 2026</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Flat price for S/M and L/XL sizes</t>
+    <t>Flat price across S/M and L/XL sizes</t>
   </si>
   <si>
     <t>0.20</t>
@@ -121,7 +114,7 @@
     <t>Sizes</t>
   </si>
   <si>
-    <t>Cord / thread type</t>
+    <t>Cord / thread</t>
   </si>
   <si>
     <t>Housing / metal</t>
@@ -133,10 +126,7 @@
     <t>Shapes</t>
   </si>
   <si>
-    <t>Attached / Detached</t>
-  </si>
-  <si>
-    <t>Packshot images from</t>
+    <t>Packshots reuse</t>
   </si>
   <si>
     <t>Colour count</t>
@@ -157,7 +147,7 @@
     <t>Nylon</t>
   </si>
   <si>
-    <t>Standard — Yellow, White, Pink</t>
+    <t>Metal — Yellow / White / Pink</t>
   </si>
   <si>
     <t>Yellow | White | Pink</t>
@@ -172,15 +162,12 @@
     <t>0.15, 0.30, 0.60</t>
   </si>
   <si>
-    <t>Multi Three — Attached or Not Attached</t>
+    <t>Multi housing — Attached or Not Attached</t>
   </si>
   <si>
     <t>Attached: WWW, YYY, PPP | Not attached: WWW, YYY, PPP, YWP</t>
   </si>
   <si>
-    <t>Attached (F) or Not Attached (NF)</t>
-  </si>
-  <si>
     <t>M3</t>
   </si>
   <si>
@@ -190,7 +177,7 @@
     <t>0.20, 0.40</t>
   </si>
   <si>
-    <t>Gold metal — White, Yellow, Pink</t>
+    <t>Metal — White / Yellow / Pink</t>
   </si>
   <si>
     <t>White | Yellow | Pink</t>
@@ -208,10 +195,10 @@
     <t>Shine</t>
   </si>
   <si>
-    <t>No metal housing (shape + colour only)</t>
-  </si>
-  <si>
-    <t>— (no bezel/prong metal; shapes selectable directly)</t>
+    <t>Bezel / Prong + metal (Yellow / White / Pink)</t>
+  </si>
+  <si>
+    <t>Bezel: Yellow, White, Pink | Prong: Yellow, White, Pink</t>
   </si>
   <si>
     <t>Heart, Pear, Marquise, Oval, Emerald, Cushion, Long Cushion</t>
@@ -229,82 +216,70 @@
     <t>Colour name</t>
   </si>
   <si>
-    <t>Palette group</t>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>Dark Pink</t>
+  </si>
+  <si>
+    <t>Light Pink</t>
+  </si>
+  <si>
+    <t>Fluo Pink</t>
   </si>
   <si>
     <t>Orange</t>
   </si>
   <si>
-    <t>CUTY necklace palette</t>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Fluo Yellow</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Turquoise</t>
   </si>
   <si>
     <t>Light Blue</t>
   </si>
   <si>
+    <t>Royal Blue</t>
+  </si>
+  <si>
+    <t>Navy Blue</t>
+  </si>
+  <si>
+    <t>Lilac</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
     <t>Black</t>
   </si>
   <si>
-    <t>Fluo Pink</t>
-  </si>
-  <si>
-    <t>Fluo Yellow</t>
-  </si>
-  <si>
-    <t>Light Pink</t>
+    <t>Silver Grey</t>
+  </si>
+  <si>
+    <t>White</t>
   </si>
   <si>
     <t>Ivory</t>
   </si>
   <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Silver Grey</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Multi Three / Four palette</t>
-  </si>
-  <si>
-    <t>Bordeaux</t>
-  </si>
-  <si>
-    <t>Navy Blue</t>
-  </si>
-  <si>
-    <t>Shapy Shine (same as CUTY necklace)</t>
-  </si>
-  <si>
-    <t>Palette name</t>
-  </si>
-  <si>
-    <t>Used by</t>
-  </si>
-  <si>
-    <t>Colours (comma-separated)</t>
-  </si>
-  <si>
-    <t>CUTY necklace / Shapy Shine necklace</t>
-  </si>
-  <si>
-    <t>CUTY NECKLACE, SHAPY SHINE NECKLACE</t>
-  </si>
-  <si>
-    <t>Orange, Light Blue, Black, Fluo Pink, Fluo Yellow, Light Pink, Ivory, Red, Gold, Silver Grey, Green</t>
-  </si>
-  <si>
-    <t>Multi Three / Multi Four necklace</t>
-  </si>
-  <si>
-    <t>MULTI THREE NECKLACE, MULTI FOUR NECKLACE</t>
-  </si>
-  <si>
-    <t>Silver Grey, Gold, Bordeaux, Red, Black, Navy Blue</t>
+    <t>Turq Blue</t>
   </si>
   <si>
     <t>Size code</t>
@@ -322,7 +297,7 @@
     <t>S/M</t>
   </si>
   <si>
-    <t>All necklaces (CUTY, Multi Three, Multi Four, Shapy Shine)</t>
+    <t>CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, SHAPY SHINE NECKLACE</t>
   </si>
   <si>
     <t>L/XL</t>
@@ -361,21 +336,21 @@
     <t>System</t>
   </si>
   <si>
-    <t>LoveLab Mini B2B — catalog source: lib/catalog.js</t>
-  </si>
-  <si>
-    <t>All items in this file are necklaces (productType: necklace)</t>
+    <t>LoveLab Mini B2B — generated from lib/catalog.js (single source of truth)</t>
+  </si>
+  <si>
+    <t>Pricelist years</t>
+  </si>
+  <si>
+    <t>Available: 2025, 2026. Necklace prices are identical across years.</t>
+  </si>
+  <si>
+    <t>All rows are necklaces (productType: necklace)</t>
   </si>
   <si>
     <t>All necklaces are IGI only — no in-house certificate option</t>
   </si>
   <si>
-    <t>Price lists</t>
-  </si>
-  <si>
-    <t>2025 and 2026 prices are identical for all necklace SKUs</t>
-  </si>
-  <si>
     <t>Size pricing</t>
   </si>
   <si>
@@ -388,46 +363,46 @@
     <t>Retail rounded up to nearest €5 (195, 395, 540)</t>
   </si>
   <si>
-    <t>Shapy Shine necklace pricing</t>
+    <t>Shapy Shine pricing</t>
   </si>
   <si>
     <t>B2B = SSF bracelet × 1.20 (66, 120, 186). B2C = retail × 1.20 rounded up to €5 (220, 400, 540)</t>
   </si>
   <si>
-    <t>Shapy Shine colours</t>
-  </si>
-  <si>
-    <t>Same 11 cord colours as CUTY necklace (not the full 21-colour Shine bracelet palette)</t>
+    <t>CUTY &amp; Shapy Shine colours</t>
+  </si>
+  <si>
+    <t>Full cord palette available (no cap): CUTY necklace = full nylon palette, Shapy Shine necklace = full Shine palette</t>
+  </si>
+  <si>
+    <t>Multi Three / Four colours</t>
+  </si>
+  <si>
+    <t>Capped to 6 colours: Silver Grey, Gold, Bordeaux, Red, Black, Navy Blue</t>
   </si>
   <si>
     <t>Shapy Shine shapes</t>
   </si>
   <si>
-    <t>All 7 SHAPY SHINE shapes available on necklace, selectable directly after carat (see Shapy Shine shapes sheet)</t>
+    <t>All 7 shapes are selectable directly on the selection grid (one card per shape); the shape is locked per line.</t>
   </si>
   <si>
     <t>Shapy Shine housing</t>
   </si>
   <si>
-    <t>No bezel/prong metal housing on the necklace (unlike the bracelet) — config is carat -&gt; shape -&gt; colour/size</t>
+    <t>Same as the SSF bracelet: Bezel/Prong setting + metal colour (Yellow/White/Pink). At 0.10 ct only Bezel is available. Config: shape (grid) -&gt; carat -&gt; bezel/prong + metal -&gt; size -&gt; colour.</t>
   </si>
   <si>
     <t>Multi Three necklace</t>
   </si>
   <si>
-    <t>Requires Attached (F) or Not Attached (NF) setting on order line</t>
+    <t>Requires Attached (F) or Not Attached (NF) setting on the order line</t>
   </si>
   <si>
     <t>Packshots</t>
   </si>
   <si>
     <t>Necklace SKUs reuse bracelet images: CUTY_NECK→CUTY, M3_NECK→M3, M4_NECK→M4, SSF_NECK→SSF</t>
-  </si>
-  <si>
-    <t>Metadata fields (orders)</t>
-  </si>
-  <si>
-    <t>Standard order PDF + documents.metadata; DZB fields separate feature for Nicolas</t>
   </si>
 </sst>
 </file>
@@ -828,7 +803,8 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="36" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,14 +862,14 @@
       <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2">
+        <v>50</v>
+      </c>
+      <c r="I2" s="2">
+        <v>50</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -904,7 +880,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -918,14 +894,14 @@
       <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2">
+        <v>88</v>
+      </c>
+      <c r="I3" s="2">
+        <v>88</v>
+      </c>
+      <c r="J3" t="s">
         <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -936,7 +912,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -950,25 +926,25 @@
       <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2">
+        <v>125</v>
+      </c>
+      <c r="I4" s="2">
+        <v>125</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -982,25 +958,25 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2">
+        <v>81</v>
+      </c>
+      <c r="I5" s="2">
+        <v>81</v>
+      </c>
+      <c r="J5" t="s">
         <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1014,25 +990,25 @@
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2">
+        <v>119</v>
+      </c>
+      <c r="I6" s="2">
+        <v>119</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1046,25 +1022,25 @@
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2">
+        <v>219</v>
+      </c>
+      <c r="I7" s="2">
+        <v>219</v>
+      </c>
+      <c r="J7" t="s">
         <v>14</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1078,25 +1054,25 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2">
+        <v>106</v>
+      </c>
+      <c r="I8" s="2">
+        <v>106</v>
+      </c>
+      <c r="J8" t="s">
         <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1110,22 +1086,22 @@
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2">
+        <v>138</v>
+      </c>
+      <c r="I9" s="2">
+        <v>138</v>
+      </c>
+      <c r="J9" t="s">
         <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1142,25 +1118,25 @@
       <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2">
+        <v>66</v>
+      </c>
+      <c r="I10" s="2">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
         <v>14</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1174,25 +1150,25 @@
       <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2">
+        <v>120</v>
+      </c>
+      <c r="I11" s="2">
+        <v>120</v>
+      </c>
+      <c r="J11" t="s">
         <v>14</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1206,14 +1182,14 @@
       <c r="G12">
         <v>2</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2">
+        <v>186</v>
+      </c>
+      <c r="I12" s="2">
+        <v>186</v>
+      </c>
+      <c r="J12" t="s">
         <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1225,73 +1201,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
-    <col min="10" max="10" width="48" customWidth="1"/>
-    <col min="11" max="11" width="52" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="11" width="52" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1299,188 +1271,176 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>44</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>46</v>
       </c>
-      <c r="J2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="N3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-      <c r="N3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>56</v>
       </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" t="s">
         <v>62</v>
       </c>
-      <c r="I5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5">
-        <v>11</v>
+      <c r="N5">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1488,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1496,10 +1456,9 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1507,19 +1466,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1527,19 +1483,16 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1547,19 +1500,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1567,19 +1517,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1587,19 +1534,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1607,19 +1551,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1627,19 +1568,16 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1647,19 +1585,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1667,19 +1602,16 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1687,19 +1619,16 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1707,19 +1636,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1727,480 +1653,748 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
         <v>82</v>
       </c>
-      <c r="F12" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43">
+        <v>9</v>
+      </c>
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="E54" t="s">
         <v>74</v>
       </c>
-      <c r="F17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55">
+        <v>21</v>
+      </c>
+      <c r="E55" t="s">
         <v>85</v>
       </c>
-      <c r="F18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30">
-        <v>6</v>
-      </c>
-      <c r="E30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32">
-        <v>8</v>
-      </c>
-      <c r="E32" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33">
-        <v>9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" t="s">
-        <v>86</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2211,52 +2405,52 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="80" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="B2">
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
         <v>93</v>
-      </c>
-      <c r="B3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2266,65 +2460,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2">
-        <v>22</v>
-      </c>
-      <c r="C2">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2343,108 +2478,108 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2453,125 +2588,125 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/_reference-materials/Necklace_Full_Spec_IT.xlsx
+++ b/_reference-materials/Necklace_Full_Spec_IT.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="163">
   <si>
     <t>Product ID</t>
   </si>
@@ -99,6 +99,39 @@
     <t>0.50</t>
   </si>
   <si>
+    <t>CUBIX_NECK</t>
+  </si>
+  <si>
+    <t>CUBIX NECKLACE</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>MF_NECK</t>
+  </si>
+  <si>
+    <t>MATCHY FANCY NECKLACE</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>SSPF_NECK</t>
+  </si>
+  <si>
+    <t>SHAPY SPARKLE NECKLACE</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>HOLY_NECK</t>
+  </si>
+  <si>
+    <t>HOLY NECKLACE</t>
+  </si>
+  <si>
     <t>Product name</t>
   </si>
   <si>
@@ -207,6 +240,57 @@
     <t>SSF</t>
   </si>
   <si>
+    <t>CUBIX</t>
+  </si>
+  <si>
+    <t>0.05, 0.10, 0.20</t>
+  </si>
+  <si>
+    <t>MATCHY FANCY (MF)</t>
+  </si>
+  <si>
+    <t>0.60, 1.00</t>
+  </si>
+  <si>
+    <t>Bezel: WW, YY, PP, WY, WP, YP | Prong: White, Yellow, Pink</t>
+  </si>
+  <si>
+    <t>Pear, Heart, Emerald</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>SHAPY SPARKLE (SSPF)</t>
+  </si>
+  <si>
+    <t>0.70, 1.00</t>
+  </si>
+  <si>
+    <t>Metal — Prong</t>
+  </si>
+  <si>
+    <t>Prong</t>
+  </si>
+  <si>
+    <t>Round, Pear, Oval, Heart, Princess, Cushion, Marquise, Emerald, Long Cushion</t>
+  </si>
+  <si>
+    <t>SSPF</t>
+  </si>
+  <si>
+    <t>HOLY (D VVS)</t>
+  </si>
+  <si>
+    <t>0.50, 0.70, 1.00</t>
+  </si>
+  <si>
+    <t>Cross, Hamsa, Star of David, Greek Cross</t>
+  </si>
+  <si>
+    <t>HOLY</t>
+  </si>
+  <si>
     <t>Cord type</t>
   </si>
   <si>
@@ -297,7 +381,7 @@
     <t>S/M</t>
   </si>
   <si>
-    <t>CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, SHAPY SHINE NECKLACE</t>
+    <t>CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, SHAPY SHINE NECKLACE, CUBIX NECKLACE, MATCHY FANCY NECKLACE, SHAPY SPARKLE NECKLACE, HOLY NECKLACE</t>
   </si>
   <si>
     <t>L/XL</t>
@@ -325,6 +409,24 @@
   </si>
   <si>
     <t>Long Cushion</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Princess</t>
+  </si>
+  <si>
+    <t>Cross</t>
+  </si>
+  <si>
+    <t>Hamsa</t>
+  </si>
+  <si>
+    <t>Star of David</t>
+  </si>
+  <si>
+    <t>Greek Cross</t>
   </si>
   <si>
     <t>Field</t>
@@ -794,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1192,6 +1294,326 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2">
+        <v>36</v>
+      </c>
+      <c r="F13" s="2">
+        <v>145</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>36</v>
+      </c>
+      <c r="I13" s="2">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2">
+        <v>48</v>
+      </c>
+      <c r="F14" s="2">
+        <v>190</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>48</v>
+      </c>
+      <c r="I14" s="2">
+        <v>48</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
+        <v>84</v>
+      </c>
+      <c r="F15" s="2">
+        <v>410</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>84</v>
+      </c>
+      <c r="I15" s="2">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2">
+        <v>240</v>
+      </c>
+      <c r="F16" s="2">
+        <v>660</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>240</v>
+      </c>
+      <c r="I16" s="2">
+        <v>240</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2">
+        <v>372</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1065</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>372</v>
+      </c>
+      <c r="I17" s="2">
+        <v>372</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2">
+        <v>288</v>
+      </c>
+      <c r="F18" s="2">
+        <v>660</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>288</v>
+      </c>
+      <c r="I18" s="2">
+        <v>288</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2">
+        <v>390</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1020</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>390</v>
+      </c>
+      <c r="I19" s="2">
+        <v>390</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2">
+        <v>312</v>
+      </c>
+      <c r="F20" s="2">
+        <v>780</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20" s="2">
+        <v>312</v>
+      </c>
+      <c r="I20" s="2">
+        <v>312</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2">
+        <v>510</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2">
+        <v>510</v>
+      </c>
+      <c r="I21" s="2">
+        <v>510</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2">
+        <v>660</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1590</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>660</v>
+      </c>
+      <c r="I22" s="2">
+        <v>660</v>
+      </c>
+      <c r="J22" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1201,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1224,43 +1646,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1271,37 +1693,37 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N2">
         <v>21</v>
@@ -1315,37 +1737,37 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N3">
         <v>6</v>
@@ -1359,37 +1781,37 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
         <v>52</v>
       </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="N4">
         <v>6</v>
@@ -1403,40 +1825,216 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="N5">
         <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +2046,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1466,13 +2064,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1483,13 +2081,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1500,13 +2098,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1517,13 +2115,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1534,13 +2132,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1551,13 +2149,13 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1568,13 +2166,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1585,13 +2183,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1602,13 +2200,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1619,13 +2217,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1636,13 +2234,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1653,13 +2251,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1670,13 +2268,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1687,13 +2285,13 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1704,13 +2302,13 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1721,13 +2319,13 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1738,13 +2336,13 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1755,13 +2353,13 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1772,13 +2370,13 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1789,13 +2387,13 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D20">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1806,13 +2404,13 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1823,13 +2421,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1840,13 +2438,13 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1857,13 +2455,13 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1874,13 +2472,13 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1891,13 +2489,13 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1908,13 +2506,13 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1925,13 +2523,13 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1942,13 +2540,13 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,13 +2557,13 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1976,13 +2574,13 @@
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,13 +2591,13 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2010,13 +2608,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2027,13 +2625,13 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D34">
         <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2044,13 +2642,13 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2061,13 +2659,13 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2078,13 +2676,13 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2095,13 +2693,13 @@
         <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2112,13 +2710,13 @@
         <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2129,13 +2727,13 @@
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D40">
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2146,13 +2744,13 @@
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D41">
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2163,13 +2761,13 @@
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D42">
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2180,13 +2778,13 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D43">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2197,13 +2795,13 @@
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D44">
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2214,13 +2812,13 @@
         <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D45">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2231,13 +2829,13 @@
         <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D46">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2248,13 +2846,13 @@
         <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D47">
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2265,13 +2863,13 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D48">
         <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2282,13 +2880,13 @@
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D49">
         <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2299,13 +2897,13 @@
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D50">
         <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2316,13 +2914,13 @@
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D51">
         <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2333,13 +2931,13 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D52">
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2350,13 +2948,13 @@
         <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D53">
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2367,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D54">
         <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2384,13 +2982,1152 @@
         <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D55">
         <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>53</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D68">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>27</v>
+      </c>
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" t="s">
+        <v>53</v>
+      </c>
+      <c r="D70">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>53</v>
+      </c>
+      <c r="D72">
+        <v>17</v>
+      </c>
+      <c r="E72" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>27</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" t="s">
+        <v>53</v>
+      </c>
+      <c r="D73">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>53</v>
+      </c>
+      <c r="D74">
+        <v>19</v>
+      </c>
+      <c r="E74" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" t="s">
+        <v>53</v>
+      </c>
+      <c r="D75">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" t="s">
+        <v>53</v>
+      </c>
+      <c r="D76">
+        <v>21</v>
+      </c>
+      <c r="E76" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" t="s">
+        <v>53</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" t="s">
+        <v>53</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>53</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+      <c r="E82" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>53</v>
+      </c>
+      <c r="D83">
+        <v>7</v>
+      </c>
+      <c r="E83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" t="s">
+        <v>53</v>
+      </c>
+      <c r="D85">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>53</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
+      </c>
+      <c r="E86" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" t="s">
+        <v>53</v>
+      </c>
+      <c r="D87">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" t="s">
+        <v>53</v>
+      </c>
+      <c r="D90">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" t="s">
+        <v>53</v>
+      </c>
+      <c r="D91">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" t="s">
+        <v>53</v>
+      </c>
+      <c r="D92">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" t="s">
+        <v>53</v>
+      </c>
+      <c r="D93">
+        <v>17</v>
+      </c>
+      <c r="E93" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" t="s">
+        <v>53</v>
+      </c>
+      <c r="D94">
+        <v>18</v>
+      </c>
+      <c r="E94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" t="s">
+        <v>53</v>
+      </c>
+      <c r="D95">
+        <v>19</v>
+      </c>
+      <c r="E95" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" t="s">
+        <v>53</v>
+      </c>
+      <c r="D96">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" t="s">
+        <v>53</v>
+      </c>
+      <c r="D97">
+        <v>21</v>
+      </c>
+      <c r="E97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" t="s">
+        <v>69</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" t="s">
+        <v>69</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" t="s">
+        <v>69</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" t="s">
+        <v>69</v>
+      </c>
+      <c r="D102">
+        <v>5</v>
+      </c>
+      <c r="E102" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>33</v>
+      </c>
+      <c r="B103" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" t="s">
+        <v>69</v>
+      </c>
+      <c r="D103">
+        <v>6</v>
+      </c>
+      <c r="E103" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" t="s">
+        <v>69</v>
+      </c>
+      <c r="D104">
+        <v>7</v>
+      </c>
+      <c r="E104" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" t="s">
+        <v>34</v>
+      </c>
+      <c r="C105" t="s">
+        <v>69</v>
+      </c>
+      <c r="D105">
+        <v>8</v>
+      </c>
+      <c r="E105" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" t="s">
+        <v>69</v>
+      </c>
+      <c r="D106">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>33</v>
+      </c>
+      <c r="B107" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" t="s">
+        <v>69</v>
+      </c>
+      <c r="D107">
+        <v>10</v>
+      </c>
+      <c r="E107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" t="s">
+        <v>69</v>
+      </c>
+      <c r="D108">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" t="s">
+        <v>69</v>
+      </c>
+      <c r="D109">
+        <v>12</v>
+      </c>
+      <c r="E109" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D110">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>69</v>
+      </c>
+      <c r="D111">
+        <v>14</v>
+      </c>
+      <c r="E111" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>33</v>
+      </c>
+      <c r="B112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" t="s">
+        <v>69</v>
+      </c>
+      <c r="D112">
+        <v>15</v>
+      </c>
+      <c r="E112" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" t="s">
+        <v>69</v>
+      </c>
+      <c r="D114">
+        <v>17</v>
+      </c>
+      <c r="E114" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" t="s">
+        <v>34</v>
+      </c>
+      <c r="C115" t="s">
+        <v>69</v>
+      </c>
+      <c r="D115">
+        <v>18</v>
+      </c>
+      <c r="E115" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" t="s">
+        <v>69</v>
+      </c>
+      <c r="D116">
+        <v>19</v>
+      </c>
+      <c r="E116" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
+        <v>34</v>
+      </c>
+      <c r="C117" t="s">
+        <v>69</v>
+      </c>
+      <c r="D117">
+        <v>20</v>
+      </c>
+      <c r="E117" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
+        <v>34</v>
+      </c>
+      <c r="C118" t="s">
+        <v>69</v>
+      </c>
+      <c r="D118">
+        <v>21</v>
+      </c>
+      <c r="E118" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>36</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119" t="s">
+        <v>69</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>36</v>
+      </c>
+      <c r="B120" t="s">
+        <v>37</v>
+      </c>
+      <c r="C120" t="s">
+        <v>69</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>36</v>
+      </c>
+      <c r="B121" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" t="s">
+        <v>69</v>
+      </c>
+      <c r="D121">
+        <v>3</v>
+      </c>
+      <c r="E121" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>36</v>
+      </c>
+      <c r="B122" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" t="s">
+        <v>69</v>
+      </c>
+      <c r="D122">
+        <v>4</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2413,21 +4150,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="B2">
         <v>22</v>
@@ -2436,12 +4173,12 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>24</v>
@@ -2450,7 +4187,7 @@
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2461,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2478,10 +4215,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2495,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2509,7 +4246,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2523,7 +4260,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2537,7 +4274,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2551,7 +4288,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2565,7 +4302,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2579,7 +4316,231 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2599,34 +4560,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2634,79 +4595,79 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/_reference-materials/Necklace_Full_Spec_IT.xlsx
+++ b/_reference-materials/Necklace_Full_Spec_IT.xlsx
@@ -4,19 +4,87 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Prices" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Products" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Cord colours" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Sizes" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Shapes" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Notes for IT" state="visible" r:id="rId9"/>
+    <sheet sheetId="1" name="Overview" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Prices" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Products" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Specialities" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Cord colours" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Sizes" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Shapes" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Notes for IT" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="212">
+  <si>
+    <t>LoveLab — Necklaces full reference</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Live app catalogue (lib/catalog.js) — always in sync with the builder</t>
+  </si>
+  <si>
+    <t>Collections</t>
+  </si>
+  <si>
+    <t>9 necklaces: CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, MULTI FIVE NECKLACE, SHAPY SHINE NECKLACE, CUBIX NECKLACE, MATCHY FANCY NECKLACE, SHAPY SPARKLE NECKLACE, HOLY NECKLACE</t>
+  </si>
+  <si>
+    <t>Sheet: Prices</t>
+  </si>
+  <si>
+    <t>Every product × carat with B2B (wholesale) and B2C (retail) prices, min order qty, both price-list years.</t>
+  </si>
+  <si>
+    <t>Sheet: Products</t>
+  </si>
+  <si>
+    <t>One row per necklace: certificate, carats, sizes, cord, housing, shapes, colour count + specialities.</t>
+  </si>
+  <si>
+    <t>Sheet: Specialities</t>
+  </si>
+  <si>
+    <t>The specific rules per necklace (colour caps, prong-only, attached/detached, etc.).</t>
+  </si>
+  <si>
+    <t>Sheet: Cord colours</t>
+  </si>
+  <si>
+    <t>The full colour list available for each necklace.</t>
+  </si>
+  <si>
+    <t>Sheet: Sizes</t>
+  </si>
+  <si>
+    <t>The two necklace sizes with their cm measurements.</t>
+  </si>
+  <si>
+    <t>Sheet: Shapes</t>
+  </si>
+  <si>
+    <t>The shape options for the shape-based necklaces.</t>
+  </si>
+  <si>
+    <t>Sheet: Notes</t>
+  </si>
+  <si>
+    <t>Pricing rules and product notes.</t>
+  </si>
   <si>
     <t>Product ID</t>
   </si>
@@ -90,15 +158,24 @@
     <t>0.40</t>
   </si>
   <si>
+    <t>M5_NECK</t>
+  </si>
+  <si>
+    <t>MULTI FIVE NECKLACE</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
     <t>SSF_NECK</t>
   </si>
   <si>
     <t>SHAPY SHINE NECKLACE</t>
   </si>
   <si>
-    <t>0.50</t>
-  </si>
-  <si>
     <t>CUBIX_NECK</t>
   </si>
   <si>
@@ -165,6 +242,9 @@
     <t>Colour count</t>
   </si>
   <si>
+    <t>Specialities / specifics</t>
+  </si>
+  <si>
     <t>CUTY</t>
   </si>
   <si>
@@ -189,6 +269,9 @@
     <t>—</t>
   </si>
   <si>
+    <t>Full nylon colour palette (no cap). Metal housing Yellow / White / Pink.</t>
+  </si>
+  <si>
     <t>MULTI THREE (M3)</t>
   </si>
   <si>
@@ -204,6 +287,9 @@
     <t>M3</t>
   </si>
   <si>
+    <t>Order line must choose Attached (F) or Not Attached (NF). Colours capped to 6. Multi-row housing (WWW/YYY/PPP, + YWP when detached).</t>
+  </si>
+  <si>
     <t>MULTI FOUR (M4)</t>
   </si>
   <si>
@@ -219,15 +305,24 @@
     <t>M4</t>
   </si>
   <si>
+    <t>Colours capped to 6. Gold-metal housing (Yellow / White / Pink).</t>
+  </si>
+  <si>
+    <t>MULTI FIVE (M5)</t>
+  </si>
+  <si>
+    <t>0.25, 0.50</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
     <t>SHAPY SHINE FANCY (SSF)</t>
   </si>
   <si>
     <t>0.10, 0.30, 0.50</t>
   </si>
   <si>
-    <t>Shine</t>
-  </si>
-  <si>
     <t>Bezel / Prong + metal (Yellow / White / Pink)</t>
   </si>
   <si>
@@ -240,12 +335,18 @@
     <t>SSF</t>
   </si>
   <si>
+    <t>All 7 Shapy Shine shapes (shape chosen first, locked per line). Bezel / Prong setting — Bezel only at 0.10 ct, Bezel + Prong from 0.30 ct. Full nylon palette (necklaces are nylon-only).</t>
+  </si>
+  <si>
     <t>CUBIX</t>
   </si>
   <si>
     <t>0.05, 0.10, 0.20</t>
   </si>
   <si>
+    <t>Full nylon colour palette (no cap). Gold-metal housing.</t>
+  </si>
+  <si>
     <t>MATCHY FANCY (MF)</t>
   </si>
   <si>
@@ -261,6 +362,9 @@
     <t>MF</t>
   </si>
   <si>
+    <t>Matchy shapes (Pear / Heart / Emerald). Bezel / Prong setting. Full nylon palette.</t>
+  </si>
+  <si>
     <t>SHAPY SPARKLE (SSPF)</t>
   </si>
   <si>
@@ -279,6 +383,9 @@
     <t>SSPF</t>
   </si>
   <si>
+    <t>PRONG only (no bezel). Exists ONLY in 0.70 &amp; 1.00 ct, IGI. Nylon thread (NOT silk). All Shapy Sparkle shapes.</t>
+  </si>
+  <si>
     <t>HOLY (D VVS)</t>
   </si>
   <si>
@@ -291,6 +398,27 @@
     <t>HOLY</t>
   </si>
   <si>
+    <t>Nylon thread (NOT silk). Colours capped to 4: Silver Grey, Black, Red, Ivory. Holy shapes (Cross / Hamsa / Star of David / Greek Cross).</t>
+  </si>
+  <si>
+    <t>Carats</t>
+  </si>
+  <si>
+    <t>Colours</t>
+  </si>
+  <si>
+    <t>Speciality / specifics</t>
+  </si>
+  <si>
+    <t>21 (full Nylon palette)</t>
+  </si>
+  <si>
+    <t>6 (capped)</t>
+  </si>
+  <si>
+    <t>4 (capped)</t>
+  </si>
+  <si>
     <t>Cord type</t>
   </si>
   <si>
@@ -363,9 +491,6 @@
     <t>Ivory</t>
   </si>
   <si>
-    <t>Turq Blue</t>
-  </si>
-  <si>
     <t>Size code</t>
   </si>
   <si>
@@ -381,7 +506,7 @@
     <t>S/M</t>
   </si>
   <si>
-    <t>CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, SHAPY SHINE NECKLACE, CUBIX NECKLACE, MATCHY FANCY NECKLACE, SHAPY SPARKLE NECKLACE, HOLY NECKLACE</t>
+    <t>CUTY NECKLACE, MULTI THREE NECKLACE, MULTI FOUR NECKLACE, MULTI FIVE NECKLACE, SHAPY SHINE NECKLACE, CUBIX NECKLACE, MATCHY FANCY NECKLACE, SHAPY SPARKLE NECKLACE, HOLY NECKLACE</t>
   </si>
   <si>
     <t>L/XL</t>
@@ -444,7 +569,7 @@
     <t>Pricelist years</t>
   </si>
   <si>
-    <t>Available: 2025, 2026. Necklace prices are identical across years.</t>
+    <t>Available: 2025, 2026. Necklace prices are identical across both years (new products).</t>
   </si>
   <si>
     <t>All rows are necklaces (productType: necklace)</t>
@@ -459,6 +584,12 @@
     <t>B2B and B2C prices are flat — same for S/M and L/XL</t>
   </si>
   <si>
+    <t>Pricing rule (necklaces)</t>
+  </si>
+  <si>
+    <t>B2B = matching bracelet B2B × 1.20 (exact). B2C / retail = bracelet retail × 1.20 rounded UP to the nearest €5.</t>
+  </si>
+  <si>
     <t>CUTY necklace B2C</t>
   </si>
   <si>
@@ -471,10 +602,10 @@
     <t>B2B = SSF bracelet × 1.20 (66, 120, 186). B2C = retail × 1.20 rounded up to €5 (220, 400, 540)</t>
   </si>
   <si>
-    <t>CUTY &amp; Shapy Shine colours</t>
-  </si>
-  <si>
-    <t>Full cord palette available (no cap): CUTY necklace = full nylon palette, Shapy Shine necklace = full Shine palette</t>
+    <t>Necklace colours</t>
+  </si>
+  <si>
+    <t>All necklaces use the NYLON palette only. CUTY, CUBIX, MATCHY FANCY, SHAPY SHINE + SHAPY SPARKLE = full nylon palette (21). No colour cap.</t>
   </si>
   <si>
     <t>Multi Three / Four colours</t>
@@ -483,6 +614,18 @@
     <t>Capped to 6 colours: Silver Grey, Gold, Bordeaux, Red, Black, Navy Blue</t>
   </si>
   <si>
+    <t>HOLY necklace colours</t>
+  </si>
+  <si>
+    <t>Nylon thread (NOT silk), capped to 4 colours: Silver Grey, Black, Red, Ivory</t>
+  </si>
+  <si>
+    <t>Shapy Sparkle necklace</t>
+  </si>
+  <si>
+    <t>Single product. PRONG only (no bezel). Exists ONLY in 0.70 &amp; 1.00 ct, IGI. Nylon thread (NOT silk).</t>
+  </si>
+  <si>
     <t>Shapy Shine shapes</t>
   </si>
   <si>
@@ -495,6 +638,12 @@
     <t>Same as the SSF bracelet: Bezel/Prong setting + metal colour (Yellow/White/Pink). At 0.10 ct only Bezel is available. Config: shape (grid) -&gt; carat -&gt; bezel/prong + metal -&gt; size -&gt; colour.</t>
   </si>
   <si>
+    <t>Matchy Fancy necklace</t>
+  </si>
+  <si>
+    <t>Shapes: Pear / Heart / Emerald. Bezel / Prong setting (Yellow / White / Pink).</t>
+  </si>
+  <si>
     <t>Multi Three necklace</t>
   </si>
   <si>
@@ -504,7 +653,7 @@
     <t>Packshots</t>
   </si>
   <si>
-    <t>Necklace SKUs reuse bracelet images: CUTY_NECK→CUTY, M3_NECK→M3, M4_NECK→M4, SSF_NECK→SSF</t>
+    <t>Necklace SKUs reuse bracelet images: CUTY_NECK→CUTY, M3_NECK→M3, M4_NECK→M4, SSF_NECK→SSF, CUBIX_NECK→CUBIX, MF_NECK→MF, SSPF_NECK→SSPF, HOLY_NECK→HOLY</t>
   </si>
 </sst>
 </file>
@@ -551,12 +700,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -896,7 +1049,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" style="1" customWidth="1"/>
+    <col min="2" max="2" width="95" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -910,708 +1174,772 @@
     <col min="10" max="10" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3">
         <v>50</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>195</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>50</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3">
         <v>88</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>395</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>88</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
         <v>88</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3">
         <v>125</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>540</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>125</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>125</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3">
         <v>81</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>325</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>81</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>81</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3">
         <v>119</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>500</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>119</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3">
         <v>219</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>1000</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>219</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="3">
         <v>219</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3">
         <v>106</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>450</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>106</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>106</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3">
         <v>138</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>625</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>138</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>138</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="2">
-        <v>66</v>
-      </c>
-      <c r="F10" s="2">
-        <v>220</v>
+        <v>35</v>
+      </c>
+      <c r="E10" s="3">
+        <v>114</v>
+      </c>
+      <c r="F10" s="3">
+        <v>480</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10" s="2">
-        <v>66</v>
-      </c>
-      <c r="I10" s="2">
-        <v>66</v>
+      <c r="H10" s="3">
+        <v>114</v>
+      </c>
+      <c r="I10" s="3">
+        <v>114</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="2">
-        <v>120</v>
-      </c>
-      <c r="F11" s="2">
-        <v>400</v>
+        <v>35</v>
+      </c>
+      <c r="E11" s="3">
+        <v>156</v>
+      </c>
+      <c r="F11" s="3">
+        <v>700</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" s="2">
-        <v>120</v>
-      </c>
-      <c r="I11" s="2">
-        <v>120</v>
+      <c r="H11" s="3">
+        <v>156</v>
+      </c>
+      <c r="I11" s="3">
+        <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="2">
-        <v>186</v>
-      </c>
-      <c r="F12" s="2">
-        <v>540</v>
+        <v>35</v>
+      </c>
+      <c r="E12" s="3">
+        <v>66</v>
+      </c>
+      <c r="F12" s="3">
+        <v>220</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
-      <c r="H12" s="2">
-        <v>186</v>
-      </c>
-      <c r="I12" s="2">
-        <v>186</v>
+      <c r="H12" s="3">
+        <v>66</v>
+      </c>
+      <c r="I12" s="3">
+        <v>66</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3">
+        <v>120</v>
+      </c>
+      <c r="F13" s="3">
+        <v>400</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>120</v>
+      </c>
+      <c r="I13" s="3">
+        <v>120</v>
+      </c>
+      <c r="J13" t="s">
         <v>36</v>
-      </c>
-      <c r="F13" s="2">
-        <v>145</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
-        <v>36</v>
-      </c>
-      <c r="I13" s="2">
-        <v>36</v>
-      </c>
-      <c r="J13" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2">
-        <v>48</v>
-      </c>
-      <c r="F14" s="2">
-        <v>190</v>
+        <v>35</v>
+      </c>
+      <c r="E14" s="3">
+        <v>186</v>
+      </c>
+      <c r="F14" s="3">
+        <v>540</v>
       </c>
       <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2">
-        <v>48</v>
-      </c>
-      <c r="I14" s="2">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>186</v>
+      </c>
+      <c r="I14" s="3">
+        <v>186</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="2">
-        <v>84</v>
-      </c>
-      <c r="F15" s="2">
-        <v>410</v>
+        <v>35</v>
+      </c>
+      <c r="E15" s="3">
+        <v>36</v>
+      </c>
+      <c r="F15" s="3">
+        <v>145</v>
       </c>
       <c r="G15">
         <v>3</v>
       </c>
-      <c r="H15" s="2">
-        <v>84</v>
-      </c>
-      <c r="I15" s="2">
-        <v>84</v>
+      <c r="H15" s="3">
+        <v>36</v>
+      </c>
+      <c r="I15" s="3">
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="2">
-        <v>240</v>
-      </c>
-      <c r="F16" s="2">
-        <v>660</v>
+        <v>35</v>
+      </c>
+      <c r="E16" s="3">
+        <v>48</v>
+      </c>
+      <c r="F16" s="3">
+        <v>190</v>
       </c>
       <c r="G16">
-        <v>2</v>
-      </c>
-      <c r="H16" s="2">
-        <v>240</v>
-      </c>
-      <c r="I16" s="2">
-        <v>240</v>
+        <v>3</v>
+      </c>
+      <c r="H16" s="3">
+        <v>48</v>
+      </c>
+      <c r="I16" s="3">
+        <v>48</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2">
-        <v>372</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1065</v>
+        <v>35</v>
+      </c>
+      <c r="E17" s="3">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3">
+        <v>410</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2">
-        <v>372</v>
-      </c>
-      <c r="I17" s="2">
-        <v>372</v>
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>84</v>
+      </c>
+      <c r="I17" s="3">
+        <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="2">
-        <v>288</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="E18" s="3">
+        <v>240</v>
+      </c>
+      <c r="F18" s="3">
         <v>660</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
-      <c r="H18" s="2">
-        <v>288</v>
-      </c>
-      <c r="I18" s="2">
-        <v>288</v>
+      <c r="H18" s="3">
+        <v>240</v>
+      </c>
+      <c r="I18" s="3">
+        <v>240</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="2">
-        <v>390</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1020</v>
+        <v>35</v>
+      </c>
+      <c r="E19" s="3">
+        <v>372</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1065</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
-      <c r="H19" s="2">
-        <v>390</v>
-      </c>
-      <c r="I19" s="2">
-        <v>390</v>
+      <c r="H19" s="3">
+        <v>372</v>
+      </c>
+      <c r="I19" s="3">
+        <v>372</v>
       </c>
       <c r="J19" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="2">
-        <v>312</v>
-      </c>
-      <c r="F20" s="2">
-        <v>780</v>
+        <v>35</v>
+      </c>
+      <c r="E20" s="3">
+        <v>288</v>
+      </c>
+      <c r="F20" s="3">
+        <v>660</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
-      <c r="H20" s="2">
-        <v>312</v>
-      </c>
-      <c r="I20" s="2">
-        <v>312</v>
+      <c r="H20" s="3">
+        <v>288</v>
+      </c>
+      <c r="I20" s="3">
+        <v>288</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="2">
-        <v>510</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1200</v>
+      <c r="E21" s="3">
+        <v>390</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1020</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
-      <c r="H21" s="2">
-        <v>510</v>
-      </c>
-      <c r="I21" s="2">
-        <v>510</v>
+      <c r="H21" s="3">
+        <v>390</v>
+      </c>
+      <c r="I21" s="3">
+        <v>390</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="2">
-        <v>660</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1590</v>
+        <v>35</v>
+      </c>
+      <c r="E22" s="3">
+        <v>312</v>
+      </c>
+      <c r="F22" s="3">
+        <v>780</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
+        <v>312</v>
+      </c>
+      <c r="I22" s="3">
+        <v>312</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3">
+        <v>510</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>510</v>
+      </c>
+      <c r="I23" s="3">
+        <v>510</v>
+      </c>
+      <c r="J23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="3">
         <v>660</v>
       </c>
-      <c r="I22" s="2">
+      <c r="F24" s="3">
+        <v>1590</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" s="3">
         <v>660</v>
       </c>
-      <c r="J22" t="s">
-        <v>14</v>
+      <c r="I24" s="3">
+        <v>660</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1621,9 +1949,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1639,414 +1967,709 @@
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="K2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N2">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="N4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O4" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="N5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
         <v>76</v>
       </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N7">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="K8" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L8">
         <v>2</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="N8">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="K9" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="L9">
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N9">
+        <v>21</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" t="s">
+        <v>125</v>
+      </c>
+      <c r="N10">
         <v>4</v>
       </c>
+      <c r="O10" s="4" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2056,2078 +2679,2180 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>93</v>
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D14">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D17">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D19">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D34">
         <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D40">
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D48">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D50">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D51">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D53">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D55">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E59" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D62">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D66">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D67">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D68">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D69">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D71">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D72">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D74">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D75">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D76">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B78" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E78" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E82" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C86" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C87" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D87">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C88" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C89" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D89">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C90" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D90">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C91" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C92" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C93" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D93">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B94" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D94">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C95" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D95">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D96">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C97" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D97">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C98" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C100" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C101" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C102" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D103">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C104" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C105" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C106" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E106" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E107" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C108" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D108">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D109">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E109" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C110" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D110">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C111" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D111">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D112">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B113" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D113">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D114">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C115" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D115">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D116">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E116" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C117" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D117">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B118" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D118">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E119" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C120" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E120" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C121" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C122" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D122">
+        <v>19</v>
+      </c>
+      <c r="E122" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>58</v>
+      </c>
+      <c r="B123" t="s">
+        <v>59</v>
+      </c>
+      <c r="C123" t="s">
+        <v>79</v>
+      </c>
+      <c r="D123">
+        <v>20</v>
+      </c>
+      <c r="E123" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>58</v>
+      </c>
+      <c r="B124" t="s">
+        <v>59</v>
+      </c>
+      <c r="C124" t="s">
+        <v>79</v>
+      </c>
+      <c r="D124">
+        <v>21</v>
+      </c>
+      <c r="E124" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>61</v>
+      </c>
+      <c r="B125" t="s">
+        <v>62</v>
+      </c>
+      <c r="C125" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>61</v>
+      </c>
+      <c r="B126" t="s">
+        <v>62</v>
+      </c>
+      <c r="C126" t="s">
+        <v>79</v>
+      </c>
+      <c r="D126">
+        <v>2</v>
+      </c>
+      <c r="E126" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>61</v>
+      </c>
+      <c r="B127" t="s">
+        <v>62</v>
+      </c>
+      <c r="C127" t="s">
+        <v>79</v>
+      </c>
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>61</v>
+      </c>
+      <c r="B128" t="s">
+        <v>62</v>
+      </c>
+      <c r="C128" t="s">
+        <v>79</v>
+      </c>
+      <c r="D128">
         <v>4</v>
       </c>
-      <c r="E122" t="s">
-        <v>114</v>
+      <c r="E128" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4137,7 +4862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4148,23 +4873,23 @@
     <col min="4" max="4" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>119</v>
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="B2">
         <v>22</v>
@@ -4173,12 +4898,12 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="B3">
         <v>24</v>
@@ -4187,7 +4912,7 @@
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4196,7 +4921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4207,340 +4932,340 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>123</v>
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -4549,125 +5274,157 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>138</v>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
